--- a/data_kurikulum.xlsx
+++ b/data_kurikulum.xlsx
@@ -533,7 +533,7 @@
     <t>S2 Teknik Pertambangan</t>
   </si>
   <si>
-    <t>S2 Biomedik</t>
+    <t>S2 Ilmu Biomedik</t>
   </si>
   <si>
     <t>0668/UN9/SK.BAK.Ak/2025</t>
@@ -3630,7 +3630,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C6 C8:C9 C12 C18:C19 C29 C33:C34 C37 C52:C53 C55:C56 C58:C59 C65:C67 C72 C74 C76 C78 C82:C84 C93 C95 C104 C108 C115 C118" twoDigitTextYear="1"/>
+    <ignoredError sqref="C118 C115 C108 C104 C95 C93 C82:C84 C78 C76 C74 C72 C65:C67 C58:C59 C55:C56 C52:C53 C37 C33:C34 C29 C18:C19 C12 C8:C9 C6" twoDigitTextYear="1"/>
   </ignoredErrors>
 </worksheet>
 </file>